--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562428</v>
+        <v>121562430</v>
       </c>
       <c r="B2" t="n">
         <v>57355</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422088</v>
+        <v>422121</v>
       </c>
       <c r="R2" t="n">
-        <v>7051687</v>
+        <v>7051628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562431</v>
+        <v>121562432</v>
       </c>
       <c r="B3" t="n">
         <v>57355</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422258</v>
+        <v>422265</v>
       </c>
       <c r="R3" t="n">
-        <v>7051541</v>
+        <v>7051546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562432</v>
+        <v>121562431</v>
       </c>
       <c r="B4" t="n">
         <v>57355</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422265</v>
+        <v>422258</v>
       </c>
       <c r="R4" t="n">
-        <v>7051546</v>
+        <v>7051541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562430</v>
+        <v>121562429</v>
       </c>
       <c r="B5" t="n">
         <v>57355</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422121</v>
+        <v>422104</v>
       </c>
       <c r="R5" t="n">
-        <v>7051628</v>
+        <v>7051668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562429</v>
+        <v>121562428</v>
       </c>
       <c r="B6" t="n">
         <v>57355</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422104</v>
+        <v>422088</v>
       </c>
       <c r="R6" t="n">
-        <v>7051668</v>
+        <v>7051687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562430</v>
+        <v>121562431</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422121</v>
+        <v>422258</v>
       </c>
       <c r="R2" t="n">
-        <v>7051628</v>
+        <v>7051541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562432</v>
+        <v>121562428</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422265</v>
+        <v>422088</v>
       </c>
       <c r="R3" t="n">
-        <v>7051546</v>
+        <v>7051687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562431</v>
+        <v>121562429</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422258</v>
+        <v>422104</v>
       </c>
       <c r="R4" t="n">
-        <v>7051541</v>
+        <v>7051668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562429</v>
+        <v>121562430</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422104</v>
+        <v>422121</v>
       </c>
       <c r="R5" t="n">
-        <v>7051668</v>
+        <v>7051628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562428</v>
+        <v>121562432</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422088</v>
+        <v>422265</v>
       </c>
       <c r="R6" t="n">
-        <v>7051687</v>
+        <v>7051546</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562431</v>
+        <v>121562429</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422258</v>
+        <v>422104</v>
       </c>
       <c r="R2" t="n">
-        <v>7051541</v>
+        <v>7051668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562429</v>
+        <v>121562430</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422104</v>
+        <v>422121</v>
       </c>
       <c r="R4" t="n">
-        <v>7051668</v>
+        <v>7051628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562430</v>
+        <v>121562431</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422121</v>
+        <v>422258</v>
       </c>
       <c r="R5" t="n">
-        <v>7051628</v>
+        <v>7051541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562429</v>
+        <v>121562428</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422104</v>
+        <v>422088</v>
       </c>
       <c r="R2" t="n">
-        <v>7051668</v>
+        <v>7051687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562428</v>
+        <v>121562430</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422088</v>
+        <v>422121</v>
       </c>
       <c r="R3" t="n">
-        <v>7051687</v>
+        <v>7051628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562430</v>
+        <v>121562429</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422121</v>
+        <v>422104</v>
       </c>
       <c r="R4" t="n">
-        <v>7051628</v>
+        <v>7051668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562428</v>
+        <v>121562429</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422088</v>
+        <v>422104</v>
       </c>
       <c r="R2" t="n">
-        <v>7051687</v>
+        <v>7051668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562430</v>
+        <v>121562428</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422121</v>
+        <v>422088</v>
       </c>
       <c r="R3" t="n">
-        <v>7051628</v>
+        <v>7051687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562429</v>
+        <v>121562431</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422104</v>
+        <v>422258</v>
       </c>
       <c r="R4" t="n">
-        <v>7051668</v>
+        <v>7051541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562431</v>
+        <v>121562430</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422258</v>
+        <v>422121</v>
       </c>
       <c r="R5" t="n">
-        <v>7051541</v>
+        <v>7051628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562429</v>
+        <v>121562428</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422104</v>
+        <v>422088</v>
       </c>
       <c r="R2" t="n">
-        <v>7051668</v>
+        <v>7051687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562428</v>
+        <v>121562431</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422088</v>
+        <v>422258</v>
       </c>
       <c r="R3" t="n">
-        <v>7051687</v>
+        <v>7051541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562431</v>
+        <v>121562432</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422258</v>
+        <v>422265</v>
       </c>
       <c r="R4" t="n">
-        <v>7051541</v>
+        <v>7051546</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562430</v>
+        <v>121562429</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422121</v>
+        <v>422104</v>
       </c>
       <c r="R5" t="n">
-        <v>7051628</v>
+        <v>7051668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562432</v>
+        <v>121562430</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422265</v>
+        <v>422121</v>
       </c>
       <c r="R6" t="n">
-        <v>7051546</v>
+        <v>7051628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562431</v>
+        <v>121562430</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422258</v>
+        <v>422121</v>
       </c>
       <c r="R2" t="n">
-        <v>7051541</v>
+        <v>7051628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562429</v>
+        <v>121562431</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422104</v>
+        <v>422258</v>
       </c>
       <c r="R3" t="n">
-        <v>7051668</v>
+        <v>7051541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562432</v>
+        <v>121562428</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422265</v>
+        <v>422088</v>
       </c>
       <c r="R4" t="n">
-        <v>7051546</v>
+        <v>7051687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562430</v>
+        <v>121562432</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422121</v>
+        <v>422265</v>
       </c>
       <c r="R5" t="n">
-        <v>7051628</v>
+        <v>7051546</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562428</v>
+        <v>121562429</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422088</v>
+        <v>422104</v>
       </c>
       <c r="R6" t="n">
-        <v>7051687</v>
+        <v>7051668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562430</v>
+        <v>121562429</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422121</v>
+        <v>422104</v>
       </c>
       <c r="R2" t="n">
-        <v>7051628</v>
+        <v>7051668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562432</v>
+        <v>121562430</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422265</v>
+        <v>422121</v>
       </c>
       <c r="R5" t="n">
-        <v>7051546</v>
+        <v>7051628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562429</v>
+        <v>121562432</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422104</v>
+        <v>422265</v>
       </c>
       <c r="R6" t="n">
-        <v>7051668</v>
+        <v>7051546</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562429</v>
+        <v>121562430</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422104</v>
+        <v>422121</v>
       </c>
       <c r="R2" t="n">
-        <v>7051668</v>
+        <v>7051628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562431</v>
+        <v>121562432</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422258</v>
+        <v>422265</v>
       </c>
       <c r="R3" t="n">
-        <v>7051541</v>
+        <v>7051546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562428</v>
+        <v>121562431</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422088</v>
+        <v>422258</v>
       </c>
       <c r="R4" t="n">
-        <v>7051687</v>
+        <v>7051541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562430</v>
+        <v>121562429</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422121</v>
+        <v>422104</v>
       </c>
       <c r="R5" t="n">
-        <v>7051628</v>
+        <v>7051668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562432</v>
+        <v>121562428</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422265</v>
+        <v>422088</v>
       </c>
       <c r="R6" t="n">
-        <v>7051546</v>
+        <v>7051687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562430</v>
+        <v>121562428</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422121</v>
+        <v>422088</v>
       </c>
       <c r="R2" t="n">
-        <v>7051628</v>
+        <v>7051687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562431</v>
+        <v>121562429</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422258</v>
+        <v>422104</v>
       </c>
       <c r="R4" t="n">
-        <v>7051541</v>
+        <v>7051668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562429</v>
+        <v>121562431</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422104</v>
+        <v>422258</v>
       </c>
       <c r="R5" t="n">
-        <v>7051668</v>
+        <v>7051541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562428</v>
+        <v>121562430</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422088</v>
+        <v>422121</v>
       </c>
       <c r="R6" t="n">
-        <v>7051687</v>
+        <v>7051628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562428</v>
+        <v>121562431</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422088</v>
+        <v>422258</v>
       </c>
       <c r="R2" t="n">
-        <v>7051687</v>
+        <v>7051541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562432</v>
+        <v>121562429</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422265</v>
+        <v>422104</v>
       </c>
       <c r="R3" t="n">
-        <v>7051546</v>
+        <v>7051668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562429</v>
+        <v>121562432</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422104</v>
+        <v>422265</v>
       </c>
       <c r="R4" t="n">
-        <v>7051668</v>
+        <v>7051546</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562431</v>
+        <v>121562428</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422258</v>
+        <v>422088</v>
       </c>
       <c r="R5" t="n">
-        <v>7051541</v>
+        <v>7051687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50321-2024 artfynd.xlsx
+++ b/artfynd/A 50321-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121562431</v>
+        <v>121562430</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422258</v>
+        <v>422121</v>
       </c>
       <c r="R2" t="n">
-        <v>7051541</v>
+        <v>7051628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121562429</v>
+        <v>121562428</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422104</v>
+        <v>422088</v>
       </c>
       <c r="R3" t="n">
-        <v>7051668</v>
+        <v>7051687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121562432</v>
+        <v>121562429</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422265</v>
+        <v>422104</v>
       </c>
       <c r="R4" t="n">
-        <v>7051546</v>
+        <v>7051668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121562428</v>
+        <v>121562431</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422088</v>
+        <v>422258</v>
       </c>
       <c r="R5" t="n">
-        <v>7051687</v>
+        <v>7051541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121562430</v>
+        <v>121562432</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422121</v>
+        <v>422265</v>
       </c>
       <c r="R6" t="n">
-        <v>7051628</v>
+        <v>7051546</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
